--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/MARYLAND_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/MARYLAND_2018.xlsx
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C93">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C158">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C426">
